--- a/target/classes/com/mycompany/ocxrst/BASES/REGISTRORECIBIR.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/REGISTRORECIBIR.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="34">
   <si>
     <t>MODELO</t>
   </si>
@@ -115,6 +115,24 @@
   </si>
   <si>
     <t>MOUSE01</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>nest04</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>CAN001</t>
+  </si>
+  <si>
+    <t>CAN002</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
   </si>
 </sst>
 </file>
@@ -470,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5622891D-89C6-4778-AAB6-F1E7E2CFF77D}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" customWidth="true" width="15.33203125" collapsed="true"/>
@@ -868,6 +886,261 @@
         <v>5</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
